--- a/data/trans_bre/IP1002-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1002-Estudios-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 2,53</t>
+          <t>-5,6; 2,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 3,4</t>
+          <t>-4,7; 3,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 2,8</t>
+          <t>-3,09; 1,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 1,51</t>
+          <t>-5,26; 1,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-90,02; 198,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,62</t>
+          <t>-0,7; 1,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 0,55</t>
+          <t>-2,54; 0,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,98</t>
+          <t>-1,46; 0,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 1,22</t>
+          <t>-1,37; 1,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,12; 357,63</t>
+          <t>-58,57; 436,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-76,42; 36,28</t>
+          <t>-73,83; 39,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-73,0; 137,41</t>
+          <t>-73,33; 121,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,48; 170,44</t>
+          <t>-70,54; 224,28</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,58</t>
+          <t>-1,53; 1,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 0,72</t>
+          <t>-3,34; 0,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 1,17</t>
+          <t>-2,18; 1,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 2,28</t>
+          <t>-2,65; 2,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,12 +885,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 328,29</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,11</t>
+          <t>-0,77; 1,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,28</t>
+          <t>-2,12; 0,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,58</t>
+          <t>-1,24; 0,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,04</t>
+          <t>-1,48; 0,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,49; 148,97</t>
+          <t>-49,55; 163,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,67; 19,61</t>
+          <t>-69,51; 15,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-68,12; 70,29</t>
+          <t>-64,23; 74,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,5; 138,43</t>
+          <t>-66,14; 105,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1002-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1002-Estudios-trans_bre.xlsx
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 2,71</t>
+          <t>-5,82; 2,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 3,29</t>
+          <t>-5,12; 3,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 1,94</t>
+          <t>-3,1; 1,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 1,47</t>
+          <t>-5,45; 1,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,75; 273,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,83; 316,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,72</t>
+          <t>-0,54; 1,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 0,52</t>
+          <t>-2,46; 0,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,9</t>
+          <t>-1,5; 0,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,31</t>
+          <t>-1,61; 1,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,57; 436,81</t>
+          <t>-47,5; 387,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-73,83; 39,93</t>
+          <t>-74,25; 32,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-73,33; 121,62</t>
+          <t>-73,24; 125,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,54; 224,28</t>
+          <t>-76,17; 209,87</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 1,57</t>
+          <t>-1,13; 1,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,69</t>
+          <t>-3,37; 0,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 1,36</t>
+          <t>-2,15; 1,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 2,14</t>
+          <t>-2,51; 2,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,12 +885,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 1,16</t>
+          <t>-0,8; 1,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -970,32 +970,32 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,64</t>
+          <t>-1,18; 0,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,93</t>
+          <t>-1,13; 1,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,55; 163,01</t>
+          <t>-51,53; 151,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,51; 15,91</t>
+          <t>-66,39; 19,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-64,23; 74,74</t>
+          <t>-63,3; 88,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,14; 105,29</t>
+          <t>-62,08; 129,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1002-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1002-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,68</t>
+          <t>-0,85</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-48,59%</t>
+          <t>-53,97%</t>
         </is>
       </c>
     </row>
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 2,63</t>
+          <t>-6,03; 2,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 3,04</t>
+          <t>-5,03; 3,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 1,92</t>
+          <t>-3,05; 2,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 1,37</t>
+          <t>-6,32; 1,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-89,75; 273,56</t>
+          <t>-90,02; 198,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-89,83; 316,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,06</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-4,34%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,67</t>
+          <t>-0,71; 1,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,49</t>
+          <t>-2,55; 0,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,95</t>
+          <t>-1,46; 0,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,3</t>
+          <t>-1,34; 1,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,5; 387,83</t>
+          <t>-53,12; 357,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-74,25; 32,64</t>
+          <t>-76,42; 36,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-73,24; 125,91</t>
+          <t>-73,0; 137,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-76,17; 209,87</t>
+          <t>-66,51; 203,68</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>-7,76%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 1,86</t>
+          <t>-1,44; 1,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 0,75</t>
+          <t>-3,32; 0,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 1,24</t>
+          <t>-2,42; 1,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 2,31</t>
+          <t>-2,85; 2,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 328,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-6,44%</t>
+          <t>-2,69%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,18</t>
+          <t>-0,82; 1,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,25</t>
+          <t>-2,14; 0,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,7</t>
+          <t>-1,22; 0,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 1,0</t>
+          <t>-1,26; 1,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,53; 151,7</t>
+          <t>-51,49; 148,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,39; 19,04</t>
+          <t>-66,67; 19,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-63,3; 88,97</t>
+          <t>-68,12; 70,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-62,08; 129,38</t>
+          <t>-61,03; 150,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1002-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1002-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,187 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-1,15</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,85</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-29,49%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-15,68%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-5,14%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-53,97%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-1.147071025865972</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.4910238400619472</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.05151006133744581</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.8532653829254323</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.2949404290469048</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.1567528740336581</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.0514280093310321</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.5396953658467962</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-6,03; 2,53</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-5,03; 3,4</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-3,05; 2,8</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-6,32; 1,48</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-90,02; 198,51</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-6.033424629400026</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.034114345615998</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.047356017103231</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-6.319195185879284</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.9002305910867067</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.532817034371248</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.404840851313986</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.79963987397651</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1.477188722775665</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.985083163158817</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,48</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,9</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,23</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>52,5%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-36,17%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-16,29%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>6,52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,71; 1,62</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-2,55; 0,55</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,46; 0,98</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-1,34; 1,44</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-53,12; 357,63</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-76,42; 36,28</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-73,0; 137,41</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-66,51; 203,68</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.4766002737544368</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.8960853460897314</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.2260899398255445</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.08522057214372189</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.5249591605456396</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.3616849910470886</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.1629354456207544</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.06517040516573946</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,25</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>48,78%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-58,18%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-30,73%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-7,76%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.7103677483654669</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.554103106173865</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.456858527154156</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-1.337238637015542</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5311962828113362</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.7641589952096027</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.7300022903280514</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.665124184504167</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-1,44; 1,58</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,32; 0,72</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-2,42; 1,17</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-2,85; 2,11</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 328,29</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.623910316070333</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.549447189952418</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9823281784276567</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.438632093662824</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>3.576300853226061</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.3628020365238831</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.374132770777331</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>2.036772616540335</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +807,185 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,23</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,87</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,26</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,24%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-36,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-19,05%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-2,69%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.2507958823253669</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.041414272164429</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.4274350098252389</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.1276365296614178</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.4878036790388317</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.5817662341876677</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.3072534842047738</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.07757988472448159</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,82; 1,11</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,14; 0,28</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,22; 0,58</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-1,26; 1,1</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-51,49; 148,97</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-66,67; 19,61</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-68,12; 70,29</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-61,03; 150,44</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-1.437532042041481</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.319729835236661</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.4189452764889</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.850158461765975</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.58259211407132</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.7196603399656615</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.170005554463595</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.111237043849979</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="n">
+        <v>3.282855020553006</v>
+      </c>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.2270217556516199</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.868491837782834</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.2577450495145029</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.03789905998070175</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1923510620231673</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.3629382736546312</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.1905077030765089</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.02685878868061411</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.8195183841198952</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.14196630385334</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.221460862428278</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.258160875518708</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5149264143228098</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.6667411534039915</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.6811564694751115</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.6102670903000973</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.114776114007367</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.2787844723780543</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.5849691601635552</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.102876461433218</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.489676521403452</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1960522635885993</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.7029281085797116</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>1.504415029899122</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +993,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
